--- a/public/downloads/PatelGeneralizable2021.xlsx
+++ b/public/downloads/PatelGeneralizable2021.xlsx
@@ -46,10 +46,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
-  </si>
-  <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_total (ms)</t>
+  </si>
+  <si>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
